--- a/ExamSP.xlsx
+++ b/ExamSP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ztemp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\我的資料_路亞國際學校\02A.電腦課程\4000 Essential English Words 題庫系統 1.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9757D409-85A7-478F-9BF9-4EAE706B44CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A79554C-1E48-4696-9910-C875852FB3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9BA5FB67-0B6A-4DDF-A18B-E7570501EB2F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9BA5FB67-0B6A-4DDF-A18B-E7570501EB2F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="91">
   <si>
     <t>Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -230,18 +230,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>penaliz</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>cram</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>cultivat</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>defer</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -390,6 +382,10 @@
   </si>
   <si>
     <t>Some governments set rules for industries that pollute too much.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>penalize</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1023,16 +1019,16 @@
         <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>35</v>
@@ -1049,16 +1045,16 @@
         <v>26</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>50</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>28</v>
@@ -1075,16 +1071,16 @@
         <v>27</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>35</v>
@@ -1106,19 +1102,19 @@
         <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>34</v>
@@ -1132,19 +1128,19 @@
         <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>1</v>
@@ -1158,19 +1154,19 @@
         <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>28</v>
@@ -1184,19 +1180,19 @@
         <v>42</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>34</v>
@@ -1210,19 +1206,19 @@
         <v>42</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>35</v>
@@ -1233,10 +1229,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -1245,10 +1241,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G23" s="1" t="b">
         <v>1</v>
@@ -1259,10 +1255,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G24" s="1" t="b">
         <v>0</v>
@@ -1273,10 +1269,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="G25" s="1" t="b">
         <v>1</v>
